--- a/wellness_forms/019_virtual_wellness_orientation_registration_form--wellness_forms.xlsx
+++ b/wellness_forms/019_virtual_wellness_orientation_registration_form--wellness_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Time Zone</t>
+          <t>Timezone 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time Zone</t>
+          <t>Timezone 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Time Zone</t>
+          <t>Timezone 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>timezone_6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Time Zone</t>
+          <t>Timezone 6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -894,7 +894,7 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1004,7 +1004,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1038,7 +1038,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1140,7 +1140,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1208,7 +1208,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1242,7 +1242,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_5_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_5_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_5_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_5_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_6_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_6_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_6_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_6_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>timezone_6_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
